--- a/AI_MOLE/Test_Bench/Torsion_Oszillator/Experiment_log.xlsx
+++ b/AI_MOLE/Test_Bench/Torsion_Oszillator/Experiment_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programmierung_Ole\Masterarbeit_AI_MOLE\AI_MOLE\Test_Bench\Torsion_Oszillator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E482B34C-50E1-4115-9069-4348E2F305EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FBA1DA-32D0-40DF-9F97-D2CA377F14AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Versuchsprotokoll (MOLE)" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="75">
   <si>
     <t>Datum</t>
   </si>
@@ -472,8 +475,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{43DA8F1D-6502-4878-8009-693EAB99A35A}" name="Tabelle2" displayName="Tabelle2" ref="A1:G4" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A1:G4" xr:uid="{43DA8F1D-6502-4878-8009-693EAB99A35A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{43DA8F1D-6502-4878-8009-693EAB99A35A}" name="Tabelle2" displayName="Tabelle2" ref="A1:G5" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A1:G5" xr:uid="{43DA8F1D-6502-4878-8009-693EAB99A35A}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1FA48B55-6A3F-4007-B441-9696E9D798AA}" name="Dateiname" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{EDF3DA31-D44E-4CB4-A1F9-F4CABAFCB2AD}" name="Abtastzeit Ts [s]" dataDxfId="5"/>
@@ -751,23 +754,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="13.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="23" style="2" customWidth="1"/>
     <col min="7" max="7" width="22" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="30.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="30.109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -805,7 +808,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>46020</v>
       </c>
@@ -840,7 +843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>46030</v>
       </c>
@@ -878,7 +881,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>46034</v>
       </c>
@@ -916,7 +919,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>46034</v>
       </c>
@@ -954,7 +957,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>46034</v>
       </c>
@@ -992,7 +995,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>46034</v>
       </c>
@@ -1030,7 +1033,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>46035</v>
       </c>
@@ -1068,7 +1071,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>46035</v>
       </c>
@@ -1103,7 +1106,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>46035</v>
       </c>
@@ -1138,7 +1141,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>46035</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>46035</v>
       </c>
@@ -1214,7 +1217,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>46035</v>
       </c>
@@ -1252,7 +1255,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>46035</v>
       </c>
@@ -1287,7 +1290,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>46035</v>
       </c>
@@ -1322,7 +1325,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>46035</v>
       </c>
@@ -1357,7 +1360,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>46035</v>
       </c>
@@ -1392,7 +1395,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>46035</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>46036</v>
       </c>
@@ -1462,7 +1465,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>46036</v>
       </c>
@@ -1497,7 +1500,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>46036</v>
       </c>
@@ -1535,7 +1538,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>46036</v>
       </c>
@@ -1573,7 +1576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>46036</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>46036</v>
       </c>
@@ -1649,7 +1652,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>46036</v>
       </c>
@@ -1684,7 +1687,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>46036</v>
       </c>
@@ -1719,7 +1722,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>46049</v>
       </c>
@@ -1757,7 +1760,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>46049</v>
       </c>
@@ -1806,19 +1809,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9381838-4D60-4571-ADD6-94E4FB4B0EC8}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="2"/>
-    <col min="4" max="4" width="22.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="23.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="2"/>
+    <col min="4" max="4" width="22.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1841,7 +1844,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1864,7 +1867,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
@@ -1887,9 +1890,9 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="B4" s="2">
         <v>0.05</v>
@@ -1907,6 +1910,29 @@
         <v>31</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2">
+        <v>24.4</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>32</v>
       </c>
     </row>
